--- a/erp-server/erp-server-file/src/main/resources/excel/oms/B2bPlatformSkuMapping.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/B2bPlatformSkuMapping.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -106,7 +104,7 @@
     <t>{.createUserName}</t>
   </si>
   <si>
-    <t>{.createTime}</t>
+    <t>{.systemCreateTime}</t>
   </si>
   <si>
     <t>{.updateUserName}</t>
@@ -1224,28 +1222,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>